--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260608.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260608.xlsx
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>870,000</t>
+          <t>957,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>957,000</t>
+          <t>870,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
